--- a/sheets/민요/검수/뱃노래.xlsx
+++ b/sheets/민요/검수/뱃노래.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,33 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3470,8 +3577,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:S14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -3492,944 +3603,817 @@
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">뱃노래 — 민요채보-2/뱃노래.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">뱃노래</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+      <c s="8" r="R2"/>
+      <c s="8" r="S2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">담</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="O3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">백</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="P3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="Q3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="R3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="S3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="E4" s="14"/>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">려</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">잠</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">딪</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="O4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="Q4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="R4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="S4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="12"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" s="15"/>
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="I5" s="15"/>
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L5" s="12"/>
+      <c r="M5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="Q5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">누</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="R5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="S5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">누</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="12"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E6" s="13"/>
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">깨</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">치</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="Q6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="R6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="S6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="12"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="F7" s="12"/>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I7" s="14"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="N7" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="P7" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="Q7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">누</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
+      <c r="R7" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="S7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">누</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="12"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" s="15"/>
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">파</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="O8" s="15"/>
+      <c r="P8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="Q8" s="15"/>
+      <c r="R8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S8" s="2"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="S8" s="15"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="12"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E9" s="13"/>
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="K9" s="13"/>
+      <c r="L9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="N9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="O9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="R9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="12"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" s="14"/>
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="I10" s="14"/>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K10" s="14"/>
+      <c r="L10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="O10" s="14"/>
+      <c r="P10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="Q10" s="14"/>
+      <c r="R10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S10" s="14"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="12"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="N11" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O11" s="15"/>
+      <c r="P11" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="R11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="S11" s="15"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="12"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="J12" s="12"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="R12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="12"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I13" s="14"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="Q13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">차</t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="R13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
+      <c r="S13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="12"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">차</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:S2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="67"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/뱃노래.xlsx
+++ b/sheets/민요/검수/뱃노래.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -623,12 +623,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -799,12 +799,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -870,12 +870,12 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|潢</t>
+          <t xml:space="preserve">–|潢</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -945,12 +945,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I13" s="2"/>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|潢</t>
+          <t xml:space="preserve">–|潢</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I28" s="2"/>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -1719,12 +1719,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|潢</t>
+          <t xml:space="preserve">–|潢</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I37" s="2"/>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -1931,12 +1931,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I41" s="2"/>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|潢</t>
+          <t xml:space="preserve">–|潢</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I49" s="2"/>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I52" s="2"/>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I53" s="2"/>
@@ -2493,12 +2493,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -2564,12 +2564,12 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|潢</t>
+          <t xml:space="preserve">–|潢</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -2635,12 +2635,12 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I61" s="2"/>
@@ -2740,12 +2740,12 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I64" s="2"/>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I65" s="2"/>
@@ -2915,12 +2915,12 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -2986,12 +2986,12 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|潢</t>
+          <t xml:space="preserve">–|潢</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -3057,12 +3057,12 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I73" s="2"/>
@@ -3197,12 +3197,12 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -3338,12 +3338,12 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -3409,12 +3409,12 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|潢</t>
+          <t xml:space="preserve">–|潢</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I85" s="2"/>
@@ -3585,12 +3585,12 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -3621,12 +3621,12 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -3833,12 +3833,12 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I95" s="2"/>
@@ -4047,7 +4047,7 @@
       <c r="I4" s="9"/>
       <c r="J4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -4075,7 +4075,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -4088,13 +4088,13 @@
       <c r="E5" s="10"/>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="10"/>
@@ -4106,20 +4106,20 @@
       <c r="K5" s="10"/>
       <c r="L5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
       <c r="O5" s="10"/>
       <c r="P5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -4129,33 +4129,33 @@
       <c r="A6" s="0"/>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K6" s="8"/>
@@ -4284,7 +4284,7 @@
       <c r="A9" s="0"/>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -4342,49 +4342,49 @@
       <c r="C10" s="9"/>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
       <c r="G10" s="9"/>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
       <c r="K10" s="9"/>
       <c r="L10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
       <c r="M10" s="9"/>
       <c r="N10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
       <c r="O10" s="9"/>
       <c r="P10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -4445,55 +4445,55 @@
       <c r="A12" s="0"/>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
       <c r="K12" s="8"/>
       <c r="L12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
       <c r="M12" s="8"/>
       <c r="N12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -4560,43 +4560,43 @@
       <c r="C14" s="10"/>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I14" s="10"/>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K14" s="10"/>
       <c r="L14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O14" s="10"/>
       <c r="P14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q14" s="10"/>

--- a/sheets/민요/검수/뱃노래.xlsx
+++ b/sheets/민요/검수/뱃노래.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3947,659 +3985,659 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">뱃노래</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="O3" s="8"/>
-      <c r="P3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="Q3" s="8"/>
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="E3" s="22"/>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G3" s="22"/>
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I3" s="22"/>
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K3" s="22"/>
+      <c r="L3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="O3" s="22"/>
+      <c r="P3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="Q3" s="22"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="C4" s="23"/>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="E4" s="23"/>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G4" s="23"/>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I4" s="23"/>
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="Q4" s="12"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="M4" s="23"/>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="O4" s="23"/>
+      <c r="P4" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="Q4" s="25"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="26"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="26"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="G5" s="26"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="I5" s="26"/>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K5" s="26"/>
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="M5" s="26"/>
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="O5" s="26"/>
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="Q5" s="10"/>
+      <c r="Q5" s="26"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="22"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="22"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="22"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="I6" s="22"/>
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="K6" s="22"/>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O6" s="8"/>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="O6" s="22"/>
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q6" s="8"/>
+      <c r="Q6" s="22"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C7" s="23"/>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="E7" s="23"/>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="G7" s="23"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M7" s="9"/>
-      <c r="N7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="O7" s="9"/>
-      <c r="P7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="Q7" s="9"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="K7" s="23"/>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M7" s="23"/>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="O7" s="23"/>
+      <c r="P7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="Q7" s="23"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C8" s="26"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="26"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="26"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="I8" s="26"/>
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="K8" s="26"/>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="M8" s="26"/>
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O8" s="10"/>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="O8" s="26"/>
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q8" s="10"/>
+      <c r="Q8" s="26"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="C9" s="22"/>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="E9" s="22"/>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="G9" s="22"/>
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="I9" s="22"/>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="K9" s="22"/>
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M9" s="8"/>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="M9" s="22"/>
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O9" s="8"/>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="O9" s="22"/>
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q9" s="8"/>
+      <c r="Q9" s="22"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C10" s="23"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="23"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="23"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="23"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="K10" s="23"/>
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="M10" s="23"/>
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="O10" s="9"/>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="O10" s="23"/>
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="Q10" s="9"/>
+      <c r="Q10" s="23"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O11" s="10"/>
-      <c r="P11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q11" s="10"/>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C11" s="26"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E11" s="26"/>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G11" s="26"/>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I11" s="26"/>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="K11" s="26"/>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M11" s="26"/>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O11" s="26"/>
+      <c r="P11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q11" s="26"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="22"/>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="22"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="G12" s="22"/>
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="I12" s="22"/>
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="K12" s="22"/>
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="M12" s="8"/>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="M12" s="22"/>
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="O12" s="8"/>
-      <c r="P12" s="18" t="inlineStr">
+      <c r="O12" s="22"/>
+      <c r="P12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="Q12" s="11"/>
+      <c r="Q12" s="27"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O13" s="9"/>
-      <c r="P13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q13" s="9"/>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C13" s="23"/>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E13" s="23"/>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G13" s="23"/>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I13" s="23"/>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K13" s="23"/>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M13" s="23"/>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O13" s="23"/>
+      <c r="P13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q13" s="23"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="26"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="26"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="26"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="26"/>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="26"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="M14" s="26"/>
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="O14" s="26"/>
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q14" s="10"/>
+      <c r="Q14" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/뱃노래.xlsx
+++ b/sheets/민요/검수/뱃노래.xlsx
@@ -3962,28 +3962,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="Q4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
       <c r="C5" s="26"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E5" s="26"/>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="Q5" s="26"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="Q8" s="26"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="Q11" s="26"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Q12" s="27"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4588,11 +4588,11 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C14" s="26"/>

--- a/sheets/민요/검수/뱃노래.xlsx
+++ b/sheets/민요/검수/뱃노래.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -233,6 +238,21 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4013,49 +4033,49 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C3" s="22"/>
+      <c r="C3" s="28"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E3" s="22"/>
+      <c r="E3" s="28"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G3" s="22"/>
+      <c r="G3" s="28"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I3" s="22"/>
+      <c r="I3" s="28"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K3" s="22"/>
+      <c r="K3" s="28"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M3" s="22"/>
+      <c r="M3" s="28"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O3" s="22"/>
+      <c r="O3" s="28"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q3" s="22"/>
+      <c r="Q3" s="28"/>
     </row>
     <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
@@ -4064,50 +4084,50 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C4" s="23"/>
+      <c r="C4" s="29"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="29"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G4" s="23"/>
+      <c r="G4" s="29"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I4" s="23"/>
+      <c r="I4" s="29"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="K4" s="23"/>
+      <c r="K4" s="29"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M4" s="23"/>
+      <c r="M4" s="29"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O4" s="23"/>
+      <c r="O4" s="29"/>
       <c r="P4" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q4" s="25"/>
+      <c r="Q4" s="30"/>
     </row>
     <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
@@ -4117,51 +4137,51 @@
 仲</t>
         </is>
       </c>
-      <c r="C5" s="26"/>
+      <c r="C5" s="31"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E5" s="26"/>
+      <c r="E5" s="31"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G5" s="26"/>
+      <c r="G5" s="31"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="26"/>
+      <c r="I5" s="31"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K5" s="26"/>
+      <c r="K5" s="31"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="26"/>
+      <c r="M5" s="31"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="O5" s="26"/>
+      <c r="O5" s="31"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="Q5" s="26"/>
+      <c r="Q5" s="31"/>
     </row>
     <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
@@ -4171,50 +4191,50 @@
 汰</t>
         </is>
       </c>
-      <c r="C6" s="22"/>
+      <c r="C6" s="28"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="28"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G6" s="22"/>
+      <c r="G6" s="28"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I6" s="22"/>
+      <c r="I6" s="28"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K6" s="22"/>
+      <c r="K6" s="28"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M6" s="22"/>
+      <c r="M6" s="28"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O6" s="22"/>
+      <c r="O6" s="28"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q6" s="22"/>
+      <c r="Q6" s="28"/>
     </row>
     <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
@@ -4223,49 +4243,49 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C7" s="23"/>
+      <c r="C7" s="29"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="29"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G7" s="23"/>
+      <c r="G7" s="29"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="I7" s="23"/>
+      <c r="I7" s="29"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K7" s="23"/>
+      <c r="K7" s="29"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M7" s="23"/>
+      <c r="M7" s="29"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O7" s="23"/>
+      <c r="O7" s="29"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q7" s="23"/>
+      <c r="Q7" s="29"/>
     </row>
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
@@ -4274,49 +4294,49 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C8" s="26"/>
+      <c r="C8" s="31"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E8" s="26"/>
+      <c r="E8" s="31"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="31"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I8" s="26"/>
+      <c r="I8" s="31"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K8" s="26"/>
+      <c r="K8" s="31"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M8" s="26"/>
+      <c r="M8" s="31"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O8" s="26"/>
+      <c r="O8" s="31"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q8" s="26"/>
+      <c r="Q8" s="31"/>
     </row>
     <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
@@ -4326,49 +4346,49 @@
 仲</t>
         </is>
       </c>
-      <c r="C9" s="22"/>
+      <c r="C9" s="28"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E9" s="22"/>
+      <c r="E9" s="28"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G9" s="22"/>
+      <c r="G9" s="28"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I9" s="22"/>
+      <c r="I9" s="28"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K9" s="22"/>
+      <c r="K9" s="28"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M9" s="22"/>
+      <c r="M9" s="28"/>
       <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O9" s="22"/>
+      <c r="O9" s="28"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q9" s="22"/>
+      <c r="Q9" s="28"/>
     </row>
     <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
@@ -4377,56 +4397,56 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C10" s="23"/>
+      <c r="C10" s="29"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="E10" s="23"/>
+      <c r="E10" s="29"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="G10" s="23"/>
+      <c r="G10" s="29"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="I10" s="23"/>
+      <c r="I10" s="29"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="K10" s="23"/>
+      <c r="K10" s="29"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="M10" s="23"/>
+      <c r="M10" s="29"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="O10" s="23"/>
+      <c r="O10" s="29"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="Q10" s="23"/>
+      <c r="Q10" s="29"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
@@ -4435,49 +4455,49 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C11" s="26"/>
+      <c r="C11" s="31"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E11" s="26"/>
+      <c r="E11" s="31"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G11" s="26"/>
+      <c r="G11" s="31"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I11" s="26"/>
+      <c r="I11" s="31"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K11" s="26"/>
+      <c r="K11" s="31"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M11" s="26"/>
+      <c r="M11" s="31"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O11" s="26"/>
+      <c r="O11" s="31"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q11" s="26"/>
+      <c r="Q11" s="31"/>
     </row>
     <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
@@ -4486,56 +4506,56 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C12" s="22"/>
+      <c r="C12" s="28"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="E12" s="22"/>
+      <c r="E12" s="28"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="G12" s="22"/>
+      <c r="G12" s="28"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="I12" s="22"/>
+      <c r="I12" s="28"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="K12" s="22"/>
+      <c r="K12" s="28"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="M12" s="22"/>
+      <c r="M12" s="28"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="O12" s="22"/>
+      <c r="O12" s="28"/>
       <c r="P12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="Q12" s="27"/>
+      <c r="Q12" s="32"/>
     </row>
     <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
@@ -4544,49 +4564,49 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C13" s="23"/>
+      <c r="C13" s="29"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E13" s="23"/>
+      <c r="E13" s="29"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G13" s="23"/>
+      <c r="G13" s="29"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I13" s="23"/>
+      <c r="I13" s="29"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K13" s="23"/>
+      <c r="K13" s="29"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M13" s="23"/>
+      <c r="M13" s="29"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O13" s="23"/>
+      <c r="O13" s="29"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q13" s="23"/>
+      <c r="Q13" s="29"/>
     </row>
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
@@ -4595,49 +4615,49 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C14" s="26"/>
+      <c r="C14" s="31"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E14" s="26"/>
+      <c r="E14" s="31"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="26"/>
+      <c r="G14" s="31"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I14" s="26"/>
+      <c r="I14" s="31"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="26"/>
+      <c r="K14" s="31"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M14" s="26"/>
+      <c r="M14" s="31"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O14" s="26"/>
+      <c r="O14" s="31"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q14" s="26"/>
+      <c r="Q14" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/뱃노래.xlsx
+++ b/sheets/민요/검수/뱃노래.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -226,31 +221,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -347,7 +327,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">96</t>
+          <t xml:space="preserve">82</t>
         </is>
       </c>
     </row>
@@ -359,7 +339,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
     </row>
@@ -419,7 +399,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단 제목 "뱃노래 (굿거리)". 손으로 그린 12정간 격자(굵은 선 3칸마다 → 3/4). 세로줄 중 왼쪽 2줄과 오른쪽 2줄은 완전히 비어 있어 내용 있는 가장 왼쪽 줄이 8번째(=#줄수 8이 아니라, 오른쪽부터 번호 매겨 내용은 1~8줄). 가사 칸(각 율명 줄 오른쪽 좁은 칸)은 이 파일에서 미기재(사용자 본인 자료이므로 필요 시 직접 입력). 7줄 아래 작은 "右樂古"(배성/낮은 옥타브 주석) 메모 있음. 요성·작은 꾸밈 생략. 손글씨 흘림·겹침으로 ?로 둔 칸 있음.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 상단 제목 "뱃노래 (굿거리)". 손으로 그린 12정간 격자(굵은 선 3칸마다) → 3/4·12. 오른쪽부터 7줄(맨 왼쪽 2줄은 빈 줄이라 제외). 줄1~2 후렴(에야누야누야/어기여어차), 줄3~7 사설. 南은 古처럼 흘려 씀. 氵仲 은 㳞. 줄1~2 無 옆 작은 꺾쇠는 ^.</t>
         </is>
       </c>
     </row>
@@ -615,7 +595,11 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I2" s="2"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
       <c r="J2" s="4"/>
       <c r="K2" s="2"/>
     </row>
@@ -640,22 +624,22 @@
       <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵無(潕)로도 보이나 중성 無로 판독</t>
-        </is>
-      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
+      <c r="J3" s="4"/>
       <c r="K3" s="2"/>
     </row>
     <row r="4">
@@ -681,16 +665,20 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|無</t>
+          <t xml:space="preserve">–|無^</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-無</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
+無^</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">누</t>
+        </is>
+      </c>
       <c r="J4" s="4"/>
       <c r="K4" s="2"/>
     </row>
@@ -725,7 +713,11 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I5" s="2"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
       <c r="J5" s="4"/>
       <c r="K5" s="2"/>
     </row>
@@ -760,7 +752,11 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I6" s="2"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">누</t>
+        </is>
+      </c>
       <c r="J6" s="4"/>
       <c r="K6" s="2"/>
     </row>
@@ -785,18 +781,22 @@
       <c r="F7" s="2">
         <v>2</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="4"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">古 모양, 南으로 판독</t>
+        </is>
+      </c>
       <c r="K7" s="2"/>
     </row>
     <row r="8">
@@ -822,15 +822,19 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I8" s="2"/>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
       <c r="J8" s="4"/>
       <c r="K8" s="2"/>
     </row>
@@ -857,13 +861,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|汰</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-汰</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I9" s="2"/>
@@ -891,18 +894,24 @@
       <c r="F10" s="2">
         <v>3</v>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="4"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|無|南</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">古|無|古 모양, 南|無|南으로 판독</t>
+        </is>
+      </c>
       <c r="K10" s="2"/>
     </row>
     <row r="11">
@@ -926,23 +935,18 @@
       <c r="F11" s="2">
         <v>4</v>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|潢</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-潢</t>
-        </is>
-      </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢 흘려 적힘</t>
-        </is>
-      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="4"/>
       <c r="K11" s="2"/>
     </row>
     <row r="12">
@@ -968,12 +972,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I12" s="2"/>
@@ -990,28 +994,32 @@
         </is>
       </c>
       <c r="C13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
       <c r="J13" s="4"/>
       <c r="K13" s="2"/>
     </row>
@@ -1031,22 +1039,26 @@
         <v>2</v>
       </c>
       <c r="E14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">無^</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
+          <t xml:space="preserve">無^</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
       <c r="J14" s="4"/>
       <c r="K14" s="2"/>
     </row>
@@ -1066,22 +1078,27 @@
         <v>2</v>
       </c>
       <c r="E15" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">–|無^</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I15" s="2"/>
+          <t xml:space="preserve">–
+無^</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">누</t>
+        </is>
+      </c>
       <c r="J15" s="4"/>
       <c r="K15" s="2"/>
     </row>
@@ -1101,23 +1118,26 @@
         <v>2</v>
       </c>
       <c r="E16" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|無</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-無</t>
-        </is>
-      </c>
-      <c r="I16" s="2"/>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
       <c r="J16" s="4"/>
       <c r="K16" s="2"/>
     </row>
@@ -1137,22 +1157,26 @@
         <v>2</v>
       </c>
       <c r="E17" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F17" s="2">
         <v>2</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I17" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">누</t>
+        </is>
+      </c>
       <c r="J17" s="4"/>
       <c r="K17" s="2"/>
     </row>
@@ -1172,23 +1196,27 @@
         <v>2</v>
       </c>
       <c r="E18" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" s="2">
         <v>2</v>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="4"/>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I18" s="3"/>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 칸에 : 표시(반복?)</t>
+        </is>
+      </c>
       <c r="K18" s="2"/>
     </row>
     <row r="19">
@@ -1207,22 +1235,26 @@
         <v>2</v>
       </c>
       <c r="E19" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I19" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
       <c r="J19" s="4"/>
       <c r="K19" s="2"/>
     </row>
@@ -1242,7 +1274,7 @@
         <v>2</v>
       </c>
       <c r="E20" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F20" s="2">
         <v>3</v>
@@ -1257,7 +1289,11 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I20" s="2"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기</t>
+        </is>
+      </c>
       <c r="J20" s="4"/>
       <c r="K20" s="2"/>
     </row>
@@ -1277,7 +1313,7 @@
         <v>2</v>
       </c>
       <c r="E21" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" s="2">
         <v>3</v>
@@ -1313,22 +1349,26 @@
         <v>2</v>
       </c>
       <c r="E22" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F22" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I22" s="2"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
       <c r="J22" s="4"/>
       <c r="K22" s="2"/>
     </row>
@@ -1348,7 +1388,7 @@
         <v>2</v>
       </c>
       <c r="E23" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F23" s="2">
         <v>4</v>
@@ -1364,7 +1404,11 @@
 潢</t>
         </is>
       </c>
-      <c r="I23" s="2"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
       <c r="J23" s="4"/>
       <c r="K23" s="2"/>
     </row>
@@ -1384,22 +1428,26 @@
         <v>2</v>
       </c>
       <c r="E24" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F24" s="2">
         <v>4</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I24" s="2"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">차</t>
+        </is>
+      </c>
       <c r="J24" s="4"/>
       <c r="K24" s="2"/>
     </row>
@@ -1413,28 +1461,32 @@
         </is>
       </c>
       <c r="C25" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F25" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I25" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">뱃</t>
+        </is>
+      </c>
       <c r="J25" s="4"/>
       <c r="K25" s="2"/>
     </row>
@@ -1454,7 +1506,7 @@
         <v>3</v>
       </c>
       <c r="E26" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="2">
         <v>1</v>
@@ -1469,7 +1521,11 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I26" s="2"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">놀</t>
+        </is>
+      </c>
       <c r="J26" s="4"/>
       <c r="K26" s="2"/>
     </row>
@@ -1489,22 +1545,27 @@
         <v>3</v>
       </c>
       <c r="E27" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="2">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I27" s="2"/>
+          <t xml:space="preserve">–
+南</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
       <c r="J27" s="4"/>
       <c r="K27" s="2"/>
     </row>
@@ -1524,22 +1585,26 @@
         <v>3</v>
       </c>
       <c r="E28" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I28" s="2"/>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
       <c r="J28" s="4"/>
       <c r="K28" s="2"/>
     </row>
@@ -1559,19 +1624,19 @@
         <v>3</v>
       </c>
       <c r="E29" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F29" s="2">
         <v>2</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I29" s="2"/>
@@ -1594,22 +1659,26 @@
         <v>3</v>
       </c>
       <c r="E30" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F30" s="2">
         <v>2</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I30" s="2"/>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잔</t>
+        </is>
+      </c>
       <c r="J30" s="4"/>
       <c r="K30" s="2"/>
     </row>
@@ -1629,22 +1698,26 @@
         <v>3</v>
       </c>
       <c r="E31" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F31" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I31" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
       <c r="J31" s="4"/>
       <c r="K31" s="2"/>
     </row>
@@ -1664,23 +1737,27 @@
         <v>3</v>
       </c>
       <c r="E32" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F32" s="2">
         <v>3</v>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I32" s="2"/>
-      <c r="J32" s="4"/>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I32" s="3"/>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짧은 가로획 4개(8~11), –로 판독</t>
+        </is>
+      </c>
       <c r="K32" s="2"/>
     </row>
     <row r="33">
@@ -1699,20 +1776,19 @@
         <v>3</v>
       </c>
       <c r="E33" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F33" s="2">
         <v>3</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|汰</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-汰</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I33" s="2"/>
@@ -1735,19 +1811,19 @@
         <v>3</v>
       </c>
       <c r="E34" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F34" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I34" s="2"/>
@@ -1770,20 +1846,19 @@
         <v>3</v>
       </c>
       <c r="E35" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F35" s="2">
         <v>4</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|潢</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-潢</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I35" s="2"/>
@@ -1806,19 +1881,20 @@
         <v>3</v>
       </c>
       <c r="E36" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F36" s="2">
         <v>4</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I36" s="2"/>
@@ -1835,28 +1911,32 @@
         </is>
       </c>
       <c r="C37" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F37" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I37" s="2"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부</t>
+        </is>
+      </c>
       <c r="J37" s="4"/>
       <c r="K37" s="2"/>
     </row>
@@ -1876,22 +1956,26 @@
         <v>4</v>
       </c>
       <c r="E38" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="2">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I38" s="2"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">딪</t>
+        </is>
+      </c>
       <c r="J38" s="4"/>
       <c r="K38" s="2"/>
     </row>
@@ -1911,20 +1995,19 @@
         <v>4</v>
       </c>
       <c r="E39" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" s="2">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|仲</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-仲</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I39" s="2"/>
@@ -1947,22 +2030,26 @@
         <v>4</v>
       </c>
       <c r="E40" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F40" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I40" s="2"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">치</t>
+        </is>
+      </c>
       <c r="J40" s="4"/>
       <c r="K40" s="2"/>
     </row>
@@ -1982,22 +2069,26 @@
         <v>4</v>
       </c>
       <c r="E41" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F41" s="2">
         <v>2</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I41" s="2"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는</t>
+        </is>
+      </c>
       <c r="J41" s="4"/>
       <c r="K41" s="2"/>
     </row>
@@ -2017,22 +2108,26 @@
         <v>4</v>
       </c>
       <c r="E42" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F42" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I42" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">파</t>
+        </is>
+      </c>
       <c r="J42" s="4"/>
       <c r="K42" s="2"/>
     </row>
@@ -2052,22 +2147,26 @@
         <v>4</v>
       </c>
       <c r="E43" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F43" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I43" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도</t>
+        </is>
+      </c>
       <c r="J43" s="4"/>
       <c r="K43" s="2"/>
     </row>
@@ -2087,22 +2186,27 @@
         <v>4</v>
       </c>
       <c r="E44" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F44" s="2">
         <v>3</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I44" s="2"/>
+          <t xml:space="preserve">–
+汰</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오</t>
+        </is>
+      </c>
       <c r="J44" s="4"/>
       <c r="K44" s="2"/>
     </row>
@@ -2122,23 +2226,26 @@
         <v>4</v>
       </c>
       <c r="E45" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F45" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|汰</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-汰</t>
-        </is>
-      </c>
-      <c r="I45" s="2"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소</t>
+        </is>
+      </c>
       <c r="J45" s="4"/>
       <c r="K45" s="2"/>
     </row>
@@ -2158,22 +2265,27 @@
         <v>4</v>
       </c>
       <c r="E46" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F46" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">–|潢</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I46" s="2"/>
+          <t xml:space="preserve">–
+潢</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리</t>
+        </is>
+      </c>
       <c r="J46" s="4"/>
       <c r="K46" s="2"/>
     </row>
@@ -2193,23 +2305,26 @@
         <v>4</v>
       </c>
       <c r="E47" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F47" s="2">
         <v>4</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|潢</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-潢</t>
-        </is>
-      </c>
-      <c r="I47" s="2"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
       <c r="J47" s="4"/>
       <c r="K47" s="2"/>
     </row>
@@ -2223,28 +2338,32 @@
         </is>
       </c>
       <c r="C48" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D48" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E48" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F48" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I48" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">단</t>
+        </is>
+      </c>
       <c r="J48" s="4"/>
       <c r="K48" s="2"/>
     </row>
@@ -2258,28 +2377,32 @@
         </is>
       </c>
       <c r="C49" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D49" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E49" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F49" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I49" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잠</t>
+        </is>
+      </c>
       <c r="J49" s="4"/>
       <c r="K49" s="2"/>
     </row>
@@ -2299,22 +2422,27 @@
         <v>5</v>
       </c>
       <c r="E50" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F50" s="2">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I50" s="2"/>
+          <t xml:space="preserve">–
+南</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
       <c r="J50" s="4"/>
       <c r="K50" s="2"/>
     </row>
@@ -2334,10 +2462,10 @@
         <v>5</v>
       </c>
       <c r="E51" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F51" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -2349,7 +2477,11 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I51" s="2"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">깨</t>
+        </is>
+      </c>
       <c r="J51" s="4"/>
       <c r="K51" s="2"/>
     </row>
@@ -2369,19 +2501,19 @@
         <v>5</v>
       </c>
       <c r="E52" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F52" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I52" s="2"/>
@@ -2404,22 +2536,26 @@
         <v>5</v>
       </c>
       <c r="E53" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F53" s="2">
         <v>2</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I53" s="2"/>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우</t>
+        </is>
+      </c>
       <c r="J53" s="4"/>
       <c r="K53" s="2"/>
     </row>
@@ -2439,22 +2575,26 @@
         <v>5</v>
       </c>
       <c r="E54" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F54" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃</t>
-        </is>
-      </c>
-      <c r="I54" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">니</t>
+        </is>
+      </c>
       <c r="J54" s="4"/>
       <c r="K54" s="2"/>
     </row>
@@ -2474,19 +2614,19 @@
         <v>5</v>
       </c>
       <c r="E55" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F55" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I55" s="2"/>
@@ -2509,19 +2649,19 @@
         <v>5</v>
       </c>
       <c r="E56" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F56" s="2">
         <v>3</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="I56" s="2"/>
@@ -2544,20 +2684,19 @@
         <v>5</v>
       </c>
       <c r="E57" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F57" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|汰</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-汰</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="I57" s="2"/>
@@ -2580,19 +2719,19 @@
         <v>5</v>
       </c>
       <c r="E58" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F58" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I58" s="2"/>
@@ -2615,24 +2754,28 @@
         <v>5</v>
       </c>
       <c r="E59" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F59" s="2">
         <v>4</v>
       </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|潢</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-潢</t>
-        </is>
-      </c>
-      <c r="I59" s="2"/>
-      <c r="J59" s="4"/>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·|△</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·
+△</t>
+        </is>
+      </c>
+      <c r="I59" s="3"/>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">· 아래 작은 세모</t>
+        </is>
+      </c>
       <c r="K59" s="2"/>
     </row>
     <row r="60">
@@ -2645,28 +2788,32 @@
         </is>
       </c>
       <c r="C60" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D60" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E60" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F60" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I60" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">들</t>
+        </is>
+      </c>
       <c r="J60" s="4"/>
       <c r="K60" s="2"/>
     </row>
@@ -2680,28 +2827,32 @@
         </is>
       </c>
       <c r="C61" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D61" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E61" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F61" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I61" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">려</t>
+        </is>
+      </c>
       <c r="J61" s="4"/>
       <c r="K61" s="2"/>
     </row>
@@ -2721,19 +2872,19 @@
         <v>6</v>
       </c>
       <c r="E62" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62" s="2">
         <v>1</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I62" s="2"/>
@@ -2756,22 +2907,26 @@
         <v>6</v>
       </c>
       <c r="E63" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F63" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I63" s="2"/>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오</t>
+        </is>
+      </c>
       <c r="J63" s="4"/>
       <c r="K63" s="2"/>
     </row>
@@ -2791,19 +2946,19 @@
         <v>6</v>
       </c>
       <c r="E64" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F64" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="I64" s="2"/>
@@ -2826,22 +2981,26 @@
         <v>6</v>
       </c>
       <c r="E65" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F65" s="2">
         <v>2</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I65" s="2"/>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는</t>
+        </is>
+      </c>
       <c r="J65" s="4"/>
       <c r="K65" s="2"/>
     </row>
@@ -2861,22 +3020,26 @@
         <v>6</v>
       </c>
       <c r="E66" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F66" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I66" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">노</t>
+        </is>
+      </c>
       <c r="J66" s="4"/>
       <c r="K66" s="2"/>
     </row>
@@ -2896,22 +3059,26 @@
         <v>6</v>
       </c>
       <c r="E67" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F67" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I67" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">젓</t>
+        </is>
+      </c>
       <c r="J67" s="4"/>
       <c r="K67" s="2"/>
     </row>
@@ -2931,22 +3098,27 @@
         <v>6</v>
       </c>
       <c r="E68" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F68" s="2">
         <v>3</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I68" s="2"/>
+          <t xml:space="preserve">–
+汰</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는</t>
+        </is>
+      </c>
       <c r="J68" s="4"/>
       <c r="K68" s="2"/>
     </row>
@@ -2966,23 +3138,26 @@
         <v>6</v>
       </c>
       <c r="E69" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F69" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|汰</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-汰</t>
-        </is>
-      </c>
-      <c r="I69" s="2"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소</t>
+        </is>
+      </c>
       <c r="J69" s="4"/>
       <c r="K69" s="2"/>
     </row>
@@ -3002,22 +3177,27 @@
         <v>6</v>
       </c>
       <c r="E70" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F70" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–|潢</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I70" s="2"/>
+          <t xml:space="preserve">–
+潢</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리</t>
+        </is>
+      </c>
       <c r="J70" s="4"/>
       <c r="K70" s="2"/>
     </row>
@@ -3037,23 +3217,26 @@
         <v>6</v>
       </c>
       <c r="E71" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F71" s="2">
         <v>4</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|潢</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-潢</t>
-        </is>
-      </c>
-      <c r="I71" s="2"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
       <c r="J71" s="4"/>
       <c r="K71" s="2"/>
     </row>
@@ -3067,28 +3250,32 @@
         </is>
       </c>
       <c r="C72" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D72" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E72" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F72" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I72" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">처</t>
+        </is>
+      </c>
       <c r="J72" s="4"/>
       <c r="K72" s="2"/>
     </row>
@@ -3102,28 +3289,32 @@
         </is>
       </c>
       <c r="C73" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D73" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E73" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F73" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I73" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">량</t>
+        </is>
+      </c>
       <c r="J73" s="4"/>
       <c r="K73" s="2"/>
     </row>
@@ -3143,22 +3334,27 @@
         <v>7</v>
       </c>
       <c r="E74" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F74" s="2">
         <v>1</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I74" s="2"/>
+          <t xml:space="preserve">–
+南</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도</t>
+        </is>
+      </c>
       <c r="J74" s="4"/>
       <c r="K74" s="2"/>
     </row>
@@ -3178,22 +3374,26 @@
         <v>7</v>
       </c>
       <c r="E75" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F75" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I75" s="2"/>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하</t>
+        </is>
+      </c>
       <c r="J75" s="4"/>
       <c r="K75" s="2"/>
     </row>
@@ -3213,10 +3413,10 @@
         <v>7</v>
       </c>
       <c r="E76" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F76" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
@@ -3248,23 +3448,26 @@
         <v>7</v>
       </c>
       <c r="E77" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F77" s="2">
         <v>2</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|汰</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-汰</t>
-        </is>
-      </c>
-      <c r="I77" s="2"/>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구</t>
+        </is>
+      </c>
       <c r="J77" s="4"/>
       <c r="K77" s="2"/>
     </row>
@@ -3284,10 +3487,10 @@
         <v>7</v>
       </c>
       <c r="E78" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F78" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
@@ -3299,7 +3502,11 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I78" s="2"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
       <c r="J78" s="4"/>
       <c r="K78" s="2"/>
     </row>
@@ -3319,19 +3526,19 @@
         <v>7</v>
       </c>
       <c r="E79" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F79" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I79" s="2"/>
@@ -3354,19 +3561,19 @@
         <v>7</v>
       </c>
       <c r="E80" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F80" s="2">
         <v>3</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="I80" s="2"/>
@@ -3389,20 +3596,19 @@
         <v>7</v>
       </c>
       <c r="E81" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F81" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|汰</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-汰</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="I81" s="2"/>
@@ -3425,19 +3631,19 @@
         <v>7</v>
       </c>
       <c r="E82" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F82" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I82" s="2"/>
@@ -3460,521 +3666,32 @@
         <v>7</v>
       </c>
       <c r="E83" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F83" s="2">
         <v>4</v>
       </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|潢</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-潢</t>
-        </is>
-      </c>
-      <c r="I83" s="2"/>
-      <c r="J83" s="4"/>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·|△</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·
+△</t>
+        </is>
+      </c>
+      <c r="I83" s="3"/>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">· 아래 작은 ㄱ 모양(△?)</t>
+        </is>
+      </c>
       <c r="K83" s="2"/>
     </row>
-    <row r="84">
-      <c r="A84" s="2">
-        <v>1</v>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/뱃노래.png</t>
-        </is>
-      </c>
-      <c r="C84" s="2">
-        <v>7</v>
-      </c>
-      <c r="D84" s="2">
-        <v>7</v>
-      </c>
-      <c r="E84" s="2">
-        <v>11</v>
-      </c>
-      <c r="F84" s="2">
-        <v>4</v>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I84" s="2"/>
-      <c r="J84" s="4"/>
-      <c r="K84" s="2"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2">
-        <v>1</v>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/뱃노래.png</t>
-        </is>
-      </c>
-      <c r="C85" s="2">
-        <v>7</v>
-      </c>
-      <c r="D85" s="2">
-        <v>7</v>
-      </c>
-      <c r="E85" s="2">
-        <v>12</v>
-      </c>
-      <c r="F85" s="2">
-        <v>4</v>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I85" s="2"/>
-      <c r="J85" s="4"/>
-      <c r="K85" s="2"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2">
-        <v>1</v>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/뱃노래.png</t>
-        </is>
-      </c>
-      <c r="C86" s="2">
-        <v>8</v>
-      </c>
-      <c r="D86" s="2">
-        <v>8</v>
-      </c>
-      <c r="E86" s="2">
-        <v>1</v>
-      </c>
-      <c r="F86" s="2">
-        <v>1</v>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I86" s="2"/>
-      <c r="J86" s="4"/>
-      <c r="K86" s="2"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2">
-        <v>1</v>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/뱃노래.png</t>
-        </is>
-      </c>
-      <c r="C87" s="2">
-        <v>8</v>
-      </c>
-      <c r="D87" s="2">
-        <v>8</v>
-      </c>
-      <c r="E87" s="2">
-        <v>2</v>
-      </c>
-      <c r="F87" s="2">
-        <v>1</v>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I87" s="2"/>
-      <c r="J87" s="4"/>
-      <c r="K87" s="2"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2">
-        <v>1</v>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/뱃노래.png</t>
-        </is>
-      </c>
-      <c r="C88" s="2">
-        <v>8</v>
-      </c>
-      <c r="D88" s="2">
-        <v>8</v>
-      </c>
-      <c r="E88" s="2">
-        <v>3</v>
-      </c>
-      <c r="F88" s="2">
-        <v>1</v>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|仲</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-仲</t>
-        </is>
-      </c>
-      <c r="I88" s="2"/>
-      <c r="J88" s="4"/>
-      <c r="K88" s="2"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2">
-        <v>1</v>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/뱃노래.png</t>
-        </is>
-      </c>
-      <c r="C89" s="2">
-        <v>8</v>
-      </c>
-      <c r="D89" s="2">
-        <v>8</v>
-      </c>
-      <c r="E89" s="2">
-        <v>4</v>
-      </c>
-      <c r="F89" s="2">
-        <v>2</v>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|汰</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-汰</t>
-        </is>
-      </c>
-      <c r="I89" s="2"/>
-      <c r="J89" s="4"/>
-      <c r="K89" s="2"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2">
-        <v>1</v>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/뱃노래.png</t>
-        </is>
-      </c>
-      <c r="C90" s="2">
-        <v>8</v>
-      </c>
-      <c r="D90" s="2">
-        <v>8</v>
-      </c>
-      <c r="E90" s="2">
-        <v>5</v>
-      </c>
-      <c r="F90" s="2">
-        <v>2</v>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I90" s="2"/>
-      <c r="J90" s="4"/>
-      <c r="K90" s="2"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2">
-        <v>1</v>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/뱃노래.png</t>
-        </is>
-      </c>
-      <c r="C91" s="2">
-        <v>8</v>
-      </c>
-      <c r="D91" s="2">
-        <v>8</v>
-      </c>
-      <c r="E91" s="2">
-        <v>6</v>
-      </c>
-      <c r="F91" s="2">
-        <v>2</v>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I91" s="2"/>
-      <c r="J91" s="4"/>
-      <c r="K91" s="2"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2">
-        <v>1</v>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/뱃노래.png</t>
-        </is>
-      </c>
-      <c r="C92" s="2">
-        <v>8</v>
-      </c>
-      <c r="D92" s="2">
-        <v>8</v>
-      </c>
-      <c r="E92" s="2">
-        <v>7</v>
-      </c>
-      <c r="F92" s="2">
-        <v>3</v>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|仲</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-仲</t>
-        </is>
-      </c>
-      <c r="I92" s="2"/>
-      <c r="J92" s="4"/>
-      <c r="K92" s="2"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2">
-        <v>1</v>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/뱃노래.png</t>
-        </is>
-      </c>
-      <c r="C93" s="2">
-        <v>8</v>
-      </c>
-      <c r="D93" s="2">
-        <v>8</v>
-      </c>
-      <c r="E93" s="2">
-        <v>8</v>
-      </c>
-      <c r="F93" s="2">
-        <v>3</v>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I93" s="2"/>
-      <c r="J93" s="4"/>
-      <c r="K93" s="2"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2">
-        <v>1</v>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/뱃노래.png</t>
-        </is>
-      </c>
-      <c r="C94" s="2">
-        <v>8</v>
-      </c>
-      <c r="D94" s="2">
-        <v>8</v>
-      </c>
-      <c r="E94" s="2">
-        <v>9</v>
-      </c>
-      <c r="F94" s="2">
-        <v>3</v>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I94" s="2"/>
-      <c r="J94" s="4"/>
-      <c r="K94" s="2"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2">
-        <v>1</v>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/뱃노래.png</t>
-        </is>
-      </c>
-      <c r="C95" s="2">
-        <v>8</v>
-      </c>
-      <c r="D95" s="2">
-        <v>8</v>
-      </c>
-      <c r="E95" s="2">
-        <v>10</v>
-      </c>
-      <c r="F95" s="2">
-        <v>4</v>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I95" s="2"/>
-      <c r="J95" s="4"/>
-      <c r="K95" s="2"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2">
-        <v>1</v>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/뱃노래.png</t>
-        </is>
-      </c>
-      <c r="C96" s="2">
-        <v>8</v>
-      </c>
-      <c r="D96" s="2">
-        <v>8</v>
-      </c>
-      <c r="E96" s="2">
-        <v>11</v>
-      </c>
-      <c r="F96" s="2">
-        <v>4</v>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I96" s="2"/>
-      <c r="J96" s="4"/>
-      <c r="K96" s="2"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2">
-        <v>1</v>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/뱃노래.png</t>
-        </is>
-      </c>
-      <c r="C97" s="2">
-        <v>8</v>
-      </c>
-      <c r="D97" s="2">
-        <v>8</v>
-      </c>
-      <c r="E97" s="2">
-        <v>12</v>
-      </c>
-      <c r="F97" s="2">
-        <v>4</v>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I97" s="2"/>
-      <c r="J97" s="4"/>
-      <c r="K97" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K97"/>
+  <autoFilter ref="A1:K83"/>
 </worksheet>
 </file>
 
@@ -3996,14 +3713,12 @@
     <col min="13" max="13" width="6" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="12" customWidth="1"/>
-    <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="77.61" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4023,648 +3738,777 @@
       <c r="M2" s="20"/>
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-    </row>
-    <row r="3" ht="55.19" customHeight="1">
+    </row>
+    <row r="3" ht="77.61" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C3" s="28"/>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">처</t>
+        </is>
+      </c>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E3" s="28"/>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">들</t>
+        </is>
+      </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G3" s="28"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">단</t>
+        </is>
+      </c>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I3" s="28"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부</t>
+        </is>
+      </c>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K3" s="28"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="K3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">뱃</t>
+        </is>
+      </c>
       <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M3" s="28"/>
+      <c r="M3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
       <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O3" s="28"/>
-      <c r="P3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="Q3" s="28"/>
-    </row>
-    <row r="4" ht="55.19" customHeight="1">
+      <c r="O3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="77.61" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C4" s="29"/>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">량</t>
+        </is>
+      </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E4" s="29"/>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">려</t>
+        </is>
+      </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G4" s="29"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잠</t>
+        </is>
+      </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I4" s="29"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">딪</t>
+        </is>
+      </c>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-仲</t>
-        </is>
-      </c>
-      <c r="K4" s="29"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="K4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">놀</t>
+        </is>
+      </c>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="M4" s="29"/>
+          <t xml:space="preserve">無^</t>
+        </is>
+      </c>
+      <c r="M4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
       <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O4" s="29"/>
-      <c r="P4" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="Q4" s="30"/>
-    </row>
-    <row r="5" ht="55.19" customHeight="1">
+      <c r="O4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="77.61" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-仲</t>
-        </is>
-      </c>
-      <c r="C5" s="31"/>
+南</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도</t>
+        </is>
+      </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E5" s="31"/>
+      <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">–
+南</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G5" s="31"/>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I5" s="31"/>
+      <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K5" s="31"/>
+          <t xml:space="preserve">–
+南</t>
+        </is>
+      </c>
+      <c r="K5" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M5" s="31"/>
+          <t xml:space="preserve">–
+無^</t>
+        </is>
+      </c>
+      <c r="M5" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">누</t>
+        </is>
+      </c>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-無</t>
-        </is>
-      </c>
-      <c r="O5" s="31"/>
-      <c r="P5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-無</t>
-        </is>
-      </c>
-      <c r="Q5" s="31"/>
-    </row>
-    <row r="6" ht="55.19" customHeight="1">
+無^</t>
+        </is>
+      </c>
+      <c r="O5" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">누</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="77.61" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">깨</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">치</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="M6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="O6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="77.61" customHeight="1">
+      <c r="A7" s="0"/>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C7" s="23"/>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="E7" s="23"/>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G7" s="23"/>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K7" s="23"/>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="M7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">누</t>
+        </is>
+      </c>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="O7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">누</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="77.61" customHeight="1">
+      <c r="A8" s="0"/>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우</t>
+        </is>
+      </c>
+      <c r="H8" s="21"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잔</t>
+        </is>
+      </c>
+      <c r="L8" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="M8" s="26"/>
+      <c r="N8" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O8" s="26"/>
+    </row>
+    <row r="9" ht="77.61" customHeight="1">
+      <c r="A9" s="0"/>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">노</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">니</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">파</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="77.61" customHeight="1">
+      <c r="A10" s="0"/>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C10" s="23"/>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">젓</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G10" s="23"/>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K10" s="27"/>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기</t>
+        </is>
+      </c>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O10" s="23"/>
+    </row>
+    <row r="11" ht="77.61" customHeight="1">
+      <c r="A11" s="0"/>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="C11" s="24"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="G11" s="24"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G6" s="28"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I6" s="28"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K6" s="28"/>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M6" s="28"/>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="O6" s="28"/>
-      <c r="P6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="Q6" s="28"/>
-    </row>
-    <row r="7" ht="55.19" customHeight="1">
-      <c r="A7" s="0"/>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="G7" s="29"/>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">黃</t>
-        </is>
-      </c>
-      <c r="I7" s="29"/>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="K7" s="29"/>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M7" s="29"/>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="O7" s="29"/>
-      <c r="P7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="Q7" s="29"/>
-    </row>
-    <row r="8" ht="55.19" customHeight="1">
-      <c r="A8" s="0"/>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="G8" s="31"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I8" s="31"/>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="K8" s="31"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="M8" s="31"/>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="O8" s="31"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="Q8" s="31"/>
-    </row>
-    <row r="9" ht="55.19" customHeight="1">
-      <c r="A9" s="0"/>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-仲</t>
-        </is>
-      </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E9" s="28"/>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G9" s="28"/>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I9" s="28"/>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K9" s="28"/>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M9" s="28"/>
-      <c r="N9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O9" s="28"/>
-      <c r="P9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q9" s="28"/>
-    </row>
-    <row r="10" ht="55.19" customHeight="1">
-      <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="K11" s="24"/>
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="E10" s="29"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-汰</t>
-        </is>
-      </c>
-      <c r="G10" s="29"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-汰</t>
-        </is>
-      </c>
-      <c r="I10" s="29"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-汰</t>
-        </is>
-      </c>
-      <c r="K10" s="29"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-汰</t>
-        </is>
-      </c>
-      <c r="M10" s="29"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-汰</t>
-        </is>
-      </c>
-      <c r="O10" s="29"/>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-汰</t>
-        </is>
-      </c>
-      <c r="Q10" s="29"/>
-    </row>
-    <row r="11" ht="55.19" customHeight="1">
-      <c r="A11" s="0"/>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C11" s="31"/>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G11" s="31"/>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I11" s="31"/>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="K11" s="31"/>
-      <c r="L11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M11" s="31"/>
-      <c r="N11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O11" s="31"/>
-      <c r="P11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q11" s="31"/>
-    </row>
-    <row r="12" ht="55.19" customHeight="1">
+      <c r="M11" s="24"/>
+      <c r="N11" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="O11" s="26"/>
+    </row>
+    <row r="12" ht="77.61" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="G12" s="22"/>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="K12" s="22"/>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">여</t>
+        </is>
+      </c>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O12" s="22"/>
+    </row>
+    <row r="13" ht="77.61" customHeight="1">
+      <c r="A13" s="0"/>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C13" s="23"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G13" s="23"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="G12" s="28"/>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K13" s="23"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="I12" s="28"/>
-      <c r="J12" s="21" t="inlineStr">
+      <c r="M13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O13" s="23"/>
+    </row>
+    <row r="14" ht="77.61" customHeight="1">
+      <c r="A14" s="0"/>
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢</t>
-        </is>
-      </c>
-      <c r="K12" s="28"/>
-      <c r="L12" s="21" t="inlineStr">
+△</t>
+        </is>
+      </c>
+      <c r="C14" s="26"/>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢</t>
-        </is>
-      </c>
-      <c r="M12" s="28"/>
-      <c r="N12" s="21" t="inlineStr">
+△</t>
+        </is>
+      </c>
+      <c r="G14" s="26"/>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢</t>
-        </is>
-      </c>
-      <c r="O12" s="28"/>
-      <c r="P12" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-潢</t>
-        </is>
-      </c>
-      <c r="Q12" s="32"/>
-    </row>
-    <row r="13" ht="55.19" customHeight="1">
-      <c r="A13" s="0"/>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E13" s="29"/>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G13" s="29"/>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I13" s="29"/>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K13" s="29"/>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M13" s="29"/>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O13" s="29"/>
-      <c r="P13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q13" s="29"/>
-    </row>
-    <row r="14" ht="55.19" customHeight="1">
-      <c r="A14" s="0"/>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E14" s="31"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G14" s="31"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I14" s="31"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K14" s="31"/>
+△</t>
+        </is>
+      </c>
+      <c r="K14" s="24"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M14" s="31"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="O14" s="31"/>
-      <c r="P14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q14" s="31"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="M14" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">차</t>
+        </is>
+      </c>
+      <c r="N14" s="21"/>
+      <c r="O14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B2:O2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="76"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="86"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/뱃노래.xlsx
+++ b/sheets/민요/검수/뱃노래.xlsx
@@ -399,7 +399,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 상단 제목 "뱃노래 (굿거리)". 손으로 그린 12정간 격자(굵은 선 3칸마다) → 3/4·12. 오른쪽부터 7줄(맨 왼쪽 2줄은 빈 줄이라 제외). 줄1~2 후렴(에야누야누야/어기여어차), 줄3~7 사설. 南은 古처럼 흘려 씀. 氵仲 은 㳞. 줄1~2 無 옆 작은 꺾쇠는 ^.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 상단 제목 "뱃노래 (굿거리)". 손으로 그린 12정간 격자(굵은 선 3칸마다) → 3/4·12. 오른쪽부터 7줄(맨 왼쪽 2줄은 빈 줄이라 제외). 줄1~2 후렴(에야누야누야/어기여어차), 줄3~7 사설. 南은 古처럼 흘려 씀. 氵仲 은 㳞. 줄1~2 無 옆 작은 꺾쇠는 ^. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1281,12 +1281,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1395,13 +1395,13 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|潢</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2272,13 +2272,13 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|潢</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3184,13 +3184,13 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|潢</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="M9" s="22" t="inlineStr">
@@ -4225,7 +4225,7 @@
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -4241,7 +4241,7 @@
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
@@ -4257,7 +4257,7 @@
       <c r="K10" s="27"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="M10" s="23" t="inlineStr">
@@ -4398,7 +4398,7 @@
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -4415,7 +4415,7 @@
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -4432,7 +4432,7 @@
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="M13" s="23" t="inlineStr">

--- a/sheets/민요/검수/뱃노래.xlsx
+++ b/sheets/민요/검수/뱃노래.xlsx
@@ -65,10 +65,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/뱃노래.xlsx
+++ b/sheets/민요/검수/뱃노래.xlsx
@@ -3694,6 +3694,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -3712,10 +3715,10 @@
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="77.61" customHeight="1">
+    <row r="2" ht="60.61" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3736,7 +3739,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="77.61" customHeight="1">
+    <row r="3" ht="90.2" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3809,7 +3812,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="77.61" customHeight="1">
+    <row r="4" ht="90.2" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3882,7 +3885,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="77.61" customHeight="1">
+    <row r="5" ht="90.2" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3952,7 +3955,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="77.61" customHeight="1">
+    <row r="6" ht="90.2" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4025,7 +4028,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="77.61" customHeight="1">
+    <row r="7" ht="90.2" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4082,7 +4085,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="77.61" customHeight="1">
+    <row r="8" ht="90.2" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4139,7 +4142,7 @@
       </c>
       <c r="O8" s="26"/>
     </row>
-    <row r="9" ht="77.61" customHeight="1">
+    <row r="9" ht="90.2" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4212,7 +4215,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="77.61" customHeight="1">
+    <row r="10" ht="90.2" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4269,7 +4272,7 @@
       </c>
       <c r="O10" s="23"/>
     </row>
-    <row r="11" ht="77.61" customHeight="1">
+    <row r="11" ht="90.2" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4327,7 +4330,7 @@
       </c>
       <c r="O11" s="26"/>
     </row>
-    <row r="12" ht="77.61" customHeight="1">
+    <row r="12" ht="90.2" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4384,7 +4387,7 @@
       </c>
       <c r="O12" s="22"/>
     </row>
-    <row r="13" ht="77.61" customHeight="1">
+    <row r="13" ht="90.2" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4444,7 +4447,7 @@
       </c>
       <c r="O13" s="23"/>
     </row>
-    <row r="14" ht="77.61" customHeight="1">
+    <row r="14" ht="90.2" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="25" t="inlineStr">
         <is>
@@ -4506,6 +4509,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="86"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/뱃노래.xlsx
+++ b/sheets/민요/검수/뱃노래.xlsx
@@ -3699,26 +3699,26 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="56.34" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="83.81" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="83.81" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="83.81" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="83.81" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="83.81" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="83.81" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="O8" s="26"/>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="83.81" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="83.81" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="O10" s="23"/>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="83.81" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O11" s="26"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="83.81" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="O12" s="22"/>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="83.81" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="O13" s="23"/>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="83.81" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="25" t="inlineStr">
         <is>
@@ -4509,6 +4509,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="71"/>
 </worksheet>
 </file>